--- a/artfynd/A 22645-2026 artfynd.xlsx
+++ b/artfynd/A 22645-2026 artfynd.xlsx
@@ -675,27 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130619369</v>
+        <v>130643827</v>
       </c>
       <c r="B2" t="n">
-        <v>57076</v>
+        <v>57874</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102613</v>
+        <v>100001</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -705,34 +705,30 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Vädersjön utlopp, Vädersjön, Gålsjövägen, Ång</t>
+          <t>Vädersjön utlopp, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>643596</v>
+        <v>643529</v>
       </c>
       <c r="R2" t="n">
-        <v>7011898</v>
+        <v>7011842</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -761,7 +757,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -771,7 +767,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,39 +782,39 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Thomas Birkö</t>
+          <t>Mikael Johansson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Thomas Birkö, Mikael Johansson</t>
+          <t>Mikael Johansson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130643827</v>
+        <v>130619369</v>
       </c>
       <c r="B3" t="n">
-        <v>57805</v>
+        <v>57144</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100001</v>
+        <v>102613</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -828,30 +824,34 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Vädersjön utlopp, Ång</t>
+          <t>Vädersjön utlopp, Vädersjön, Gålsjövägen, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>643529</v>
+        <v>643596</v>
       </c>
       <c r="R3" t="n">
-        <v>7011842</v>
+        <v>7011898</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,12 +905,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Mikael Johansson</t>
+          <t>Thomas Birkö</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mikael Johansson</t>
+          <t>Thomas Birkö, Mikael Johansson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 22645-2026 artfynd.xlsx
+++ b/artfynd/A 22645-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -794,27 +794,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130619369</v>
+        <v>134721727</v>
       </c>
       <c r="B3" t="n">
-        <v>57144</v>
+        <v>57860</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102613</v>
+        <v>100100</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Bivråk</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Pernis apivorus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -875,22 +875,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,10 +910,133 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
+          <t>Thomas Birkö</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>130619369</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57144</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>102613</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Orre</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lyrurus tetrix</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Vädersjön utlopp, Vädersjön, Gålsjövägen, Ång</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>643596</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7011898</v>
+      </c>
+      <c r="S4" t="n">
+        <v>50</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Boteå</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Thomas Birkö</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
           <t>Thomas Birkö, Mikael Johansson</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22645-2026 artfynd.xlsx
+++ b/artfynd/A 22645-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130643827</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -914,6 +924,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134721727</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1037,8 +1052,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130619369</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>